--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2016/PENNSYLVANIA_2016.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2016/PENNSYLVANIA_2016.xlsx
@@ -409,7 +409,7 @@
         <v>5</v>
       </c>
       <c r="D3">
-        <v>0.0009278159213212099</v>
+        <v>0.00092781592132121</v>
       </c>
     </row>
     <row r="4">
@@ -445,7 +445,7 @@
         <v>5</v>
       </c>
       <c r="D5">
-        <v>0.0009278159213212099</v>
+        <v>0.00092781592132121</v>
       </c>
     </row>
     <row r="6">
@@ -1309,7 +1309,7 @@
         <v>5</v>
       </c>
       <c r="D53">
-        <v>0.0009278159213212099</v>
+        <v>0.00092781592132121</v>
       </c>
     </row>
     <row r="54">
@@ -1561,7 +1561,7 @@
         <v>5</v>
       </c>
       <c r="D67">
-        <v>0.0009278159213212099</v>
+        <v>0.00092781592132121</v>
       </c>
     </row>
     <row r="68">
@@ -2245,7 +2245,7 @@
         <v>5</v>
       </c>
       <c r="D105">
-        <v>0.0009278159213212099</v>
+        <v>0.00092781592132121</v>
       </c>
     </row>
     <row r="106">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C184">
@@ -4333,7 +4333,7 @@
         <v>5</v>
       </c>
       <c r="D221">
-        <v>0.0009278159213212099</v>
+        <v>0.00092781592132121</v>
       </c>
     </row>
     <row r="222">
@@ -4351,7 +4351,7 @@
         <v>5</v>
       </c>
       <c r="D222">
-        <v>0.0009278159213212099</v>
+        <v>0.00092781592132121</v>
       </c>
     </row>
     <row r="223">
@@ -4477,7 +4477,7 @@
         <v>5</v>
       </c>
       <c r="D229">
-        <v>0.0009278159213212099</v>
+        <v>0.00092781592132121</v>
       </c>
     </row>
     <row r="230">
@@ -4891,7 +4891,7 @@
         <v>5</v>
       </c>
       <c r="D252">
-        <v>0.0009278159213212099</v>
+        <v>0.00092781592132121</v>
       </c>
     </row>
     <row r="253">
@@ -5089,7 +5089,7 @@
         <v>5</v>
       </c>
       <c r="D263">
-        <v>0.0009278159213212099</v>
+        <v>0.00092781592132121</v>
       </c>
     </row>
     <row r="264">
@@ -5179,7 +5179,7 @@
         <v>5</v>
       </c>
       <c r="D268">
-        <v>0.0009278159213212099</v>
+        <v>0.00092781592132121</v>
       </c>
     </row>
     <row r="269">
@@ -5197,7 +5197,7 @@
         <v>5</v>
       </c>
       <c r="D269">
-        <v>0.0009278159213212099</v>
+        <v>0.00092781592132121</v>
       </c>
     </row>
     <row r="270">
@@ -5845,7 +5845,7 @@
         <v>5</v>
       </c>
       <c r="D305">
-        <v>0.0009278159213212099</v>
+        <v>0.00092781592132121</v>
       </c>
     </row>
     <row r="306">
@@ -6115,7 +6115,7 @@
         <v>5</v>
       </c>
       <c r="D320">
-        <v>0.0009278159213212099</v>
+        <v>0.00092781592132121</v>
       </c>
     </row>
     <row r="321">
@@ -6619,7 +6619,7 @@
         <v>5</v>
       </c>
       <c r="D348">
-        <v>0.0009278159213212099</v>
+        <v>0.00092781592132121</v>
       </c>
     </row>
     <row r="349">
@@ -6961,7 +6961,7 @@
         <v>5</v>
       </c>
       <c r="D367">
-        <v>0.0009278159213212099</v>
+        <v>0.00092781592132121</v>
       </c>
     </row>
     <row r="368">
@@ -7141,7 +7141,7 @@
         <v>5</v>
       </c>
       <c r="D377">
-        <v>0.0009278159213212099</v>
+        <v>0.00092781592132121</v>
       </c>
     </row>
     <row r="378">
@@ -7339,7 +7339,7 @@
         <v>5</v>
       </c>
       <c r="D388">
-        <v>0.0009278159213212099</v>
+        <v>0.00092781592132121</v>
       </c>
     </row>
     <row r="389">
@@ -7447,7 +7447,7 @@
         <v>5</v>
       </c>
       <c r="D394">
-        <v>0.0009278159213212099</v>
+        <v>0.00092781592132121</v>
       </c>
     </row>
     <row r="395">
@@ -7699,7 +7699,7 @@
         <v>5</v>
       </c>
       <c r="D408">
-        <v>0.0009278159213212099</v>
+        <v>0.00092781592132121</v>
       </c>
     </row>
     <row r="409">
@@ -7717,7 +7717,7 @@
         <v>5</v>
       </c>
       <c r="D409">
-        <v>0.0009278159213212099</v>
+        <v>0.00092781592132121</v>
       </c>
     </row>
     <row r="410">
@@ -7771,7 +7771,7 @@
         <v>5</v>
       </c>
       <c r="D412">
-        <v>0.0009278159213212099</v>
+        <v>0.00092781592132121</v>
       </c>
     </row>
     <row r="413">
@@ -7933,7 +7933,7 @@
         <v>5</v>
       </c>
       <c r="D421">
-        <v>0.0009278159213212099</v>
+        <v>0.00092781592132121</v>
       </c>
     </row>
     <row r="422">
@@ -8023,7 +8023,7 @@
         <v>5</v>
       </c>
       <c r="D426">
-        <v>0.0009278159213212099</v>
+        <v>0.00092781592132121</v>
       </c>
     </row>
     <row r="427">
@@ -8041,7 +8041,7 @@
         <v>5</v>
       </c>
       <c r="D427">
-        <v>0.0009278159213212099</v>
+        <v>0.00092781592132121</v>
       </c>
     </row>
     <row r="428">
@@ -8221,7 +8221,7 @@
         <v>5</v>
       </c>
       <c r="D437">
-        <v>0.0009278159213212099</v>
+        <v>0.00092781592132121</v>
       </c>
     </row>
     <row r="438">
@@ -8419,7 +8419,7 @@
         <v>5</v>
       </c>
       <c r="D448">
-        <v>0.0009278159213212099</v>
+        <v>0.00092781592132121</v>
       </c>
     </row>
     <row r="449">
@@ -9013,7 +9013,7 @@
         <v>5</v>
       </c>
       <c r="D481">
-        <v>0.0009278159213212099</v>
+        <v>0.00092781592132121</v>
       </c>
     </row>
     <row r="482">
@@ -9492,7 +9492,7 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec -Distrito 08-</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C508">
@@ -9852,7 +9852,7 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C528">
@@ -9949,7 +9949,7 @@
         <v>5</v>
       </c>
       <c r="D533">
-        <v>0.0009278159213212099</v>
+        <v>0.00092781592132121</v>
       </c>
     </row>
     <row r="534">
@@ -10687,7 +10687,7 @@
         <v>5</v>
       </c>
       <c r="D574">
-        <v>0.0009278159213212099</v>
+        <v>0.00092781592132121</v>
       </c>
     </row>
     <row r="575">
@@ -10831,7 +10831,7 @@
         <v>5</v>
       </c>
       <c r="D582">
-        <v>0.0009278159213212099</v>
+        <v>0.00092781592132121</v>
       </c>
     </row>
     <row r="583">
@@ -10921,7 +10921,7 @@
         <v>5</v>
       </c>
       <c r="D587">
-        <v>0.0009278159213212099</v>
+        <v>0.00092781592132121</v>
       </c>
     </row>
     <row r="588">
@@ -11101,7 +11101,7 @@
         <v>5</v>
       </c>
       <c r="D597">
-        <v>0.0009278159213212099</v>
+        <v>0.00092781592132121</v>
       </c>
     </row>
     <row r="598">
@@ -11533,7 +11533,7 @@
         <v>5</v>
       </c>
       <c r="D621">
-        <v>0.0009278159213212099</v>
+        <v>0.00092781592132121</v>
       </c>
     </row>
     <row r="622">
@@ -11875,7 +11875,7 @@
         <v>5</v>
       </c>
       <c r="D640">
-        <v>0.0009278159213212099</v>
+        <v>0.00092781592132121</v>
       </c>
     </row>
     <row r="641">
@@ -11893,7 +11893,7 @@
         <v>5</v>
       </c>
       <c r="D641">
-        <v>0.0009278159213212099</v>
+        <v>0.00092781592132121</v>
       </c>
     </row>
     <row r="642">
@@ -11983,7 +11983,7 @@
         <v>5</v>
       </c>
       <c r="D646">
-        <v>0.0009278159213212099</v>
+        <v>0.00092781592132121</v>
       </c>
     </row>
     <row r="647">
@@ -12145,7 +12145,7 @@
         <v>5</v>
       </c>
       <c r="D655">
-        <v>0.0009278159213212099</v>
+        <v>0.00092781592132121</v>
       </c>
     </row>
     <row r="656">
@@ -12343,7 +12343,7 @@
         <v>5</v>
       </c>
       <c r="D666">
-        <v>0.0009278159213212099</v>
+        <v>0.00092781592132121</v>
       </c>
     </row>
     <row r="667">
@@ -12559,7 +12559,7 @@
         <v>5</v>
       </c>
       <c r="D678">
-        <v>0.0009278159213212099</v>
+        <v>0.00092781592132121</v>
       </c>
     </row>
     <row r="679">
@@ -12631,7 +12631,7 @@
         <v>5</v>
       </c>
       <c r="D682">
-        <v>0.0009278159213212099</v>
+        <v>0.00092781592132121</v>
       </c>
     </row>
     <row r="683">
@@ -12721,7 +12721,7 @@
         <v>5</v>
       </c>
       <c r="D687">
-        <v>0.0009278159213212099</v>
+        <v>0.00092781592132121</v>
       </c>
     </row>
     <row r="688">
@@ -13207,7 +13207,7 @@
         <v>5</v>
       </c>
       <c r="D714">
-        <v>0.0009278159213212099</v>
+        <v>0.00092781592132121</v>
       </c>
     </row>
     <row r="715">
@@ -13495,7 +13495,7 @@
         <v>5</v>
       </c>
       <c r="D730">
-        <v>0.0009278159213212099</v>
+        <v>0.00092781592132121</v>
       </c>
     </row>
     <row r="731">
@@ -13747,7 +13747,7 @@
         <v>5</v>
       </c>
       <c r="D744">
-        <v>0.0009278159213212099</v>
+        <v>0.00092781592132121</v>
       </c>
     </row>
     <row r="745">
@@ -14539,7 +14539,7 @@
         <v>5</v>
       </c>
       <c r="D788">
-        <v>0.0009278159213212099</v>
+        <v>0.00092781592132121</v>
       </c>
     </row>
     <row r="789">
@@ -14953,7 +14953,7 @@
         <v>5</v>
       </c>
       <c r="D811">
-        <v>0.0009278159213212099</v>
+        <v>0.00092781592132121</v>
       </c>
     </row>
     <row r="812">
@@ -15583,7 +15583,7 @@
         <v>5</v>
       </c>
       <c r="D846">
-        <v>0.0009278159213212099</v>
+        <v>0.00092781592132121</v>
       </c>
     </row>
     <row r="847">
@@ -15637,7 +15637,7 @@
         <v>5</v>
       </c>
       <c r="D849">
-        <v>0.0009278159213212099</v>
+        <v>0.00092781592132121</v>
       </c>
     </row>
     <row r="850">
@@ -15745,7 +15745,7 @@
         <v>5</v>
       </c>
       <c r="D855">
-        <v>0.0009278159213212099</v>
+        <v>0.00092781592132121</v>
       </c>
     </row>
     <row r="856">
@@ -15943,7 +15943,7 @@
         <v>5</v>
       </c>
       <c r="D866">
-        <v>0.0009278159213212099</v>
+        <v>0.00092781592132121</v>
       </c>
     </row>
     <row r="867">
@@ -16033,7 +16033,7 @@
         <v>5</v>
       </c>
       <c r="D871">
-        <v>0.0009278159213212099</v>
+        <v>0.00092781592132121</v>
       </c>
     </row>
     <row r="872">
@@ -16069,7 +16069,7 @@
         <v>5</v>
       </c>
       <c r="D873">
-        <v>0.0009278159213212099</v>
+        <v>0.00092781592132121</v>
       </c>
     </row>
     <row r="874">
@@ -16267,7 +16267,7 @@
         <v>5</v>
       </c>
       <c r="D884">
-        <v>0.0009278159213212099</v>
+        <v>0.00092781592132121</v>
       </c>
     </row>
     <row r="885">
@@ -16501,7 +16501,7 @@
         <v>5</v>
       </c>
       <c r="D897">
-        <v>0.0009278159213212099</v>
+        <v>0.00092781592132121</v>
       </c>
     </row>
     <row r="898">
